--- a/templates/問い合わせ台帳.xlsx
+++ b/templates/問い合わせ台帳.xlsx
@@ -16,23 +16,6 @@
     from collections import Counter
     c = Counter(v for row in r for v in row if v)
     return [[k, n] for k, n in sorted(c.items())] or [["(まだ無い)", 0]]
-</script>
-  <script name="取り込み"># フォームの受信箱(CSV を返す URL)から新着を台帳へ追記する。
-# 実行は「@取り込み net」(網あり檻 — 許可はその場の操作だけ)。
-# URL を自分のフォームのものに書き換えて使う。
-URL = "http://127.0.0.1:8000/inbox.csv"
-import urllib.request, csv, io
-raw = urllib.request.urlopen(URL, timeout=5).read()
-rows = list(csv.DictReader(io.StringIO(raw.decode("utf-8"))))
-base = len([r for r in s.values() if any(v is not None and v != "" for v in r)])
-for i, r in enumerate(rows):
-    n = base + 1 + i
-    s[f"A{n}"] = r.get("received", "")
-    s[f"B{n}"] = r.get("name", "")
-    s[f"C{n}"] = r.get("email", "")
-    s[f"D{n}"] = r.get("body", "")
-    s[f"E{n}"] = "未対応"
-print(f"{len(rows)} 件を取り込みました")
 </script>
 </joPython>
 </file>
